--- a/2022/Bekaa1/Bekaa1_members_final.xlsx
+++ b/2022/Bekaa1/Bekaa1_members_final.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>حزب سبعة</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>القوات اللبنانية</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
